--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:39:35+00:00</t>
+    <t>2026-09-30T09:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1574,7 +1574,7 @@
     <t>**AutorSpecialty**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS|20260505120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS|20260928120000</t>
   </si>
   <si>
     <t>xdmAuthorDocumentEntry</t>
@@ -1990,7 +1990,7 @@
     <t>Métadonnée contenant les informations définissant le format du document. Il précise les spécifications techniques auxquelles il est conforme</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS|20260629120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS|20260928120000</t>
   </si>
   <si>
     <t>xdmDocumentEntry.format.code</t>
@@ -2301,7 +2301,7 @@
     <t>Ensemble de métadonnées représentant le type d’activité associé à l’événement clinique ayant abouti à la constitution du lot de soumission.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J03-XdsContentTypeCode-CISIS/FHIR/JDV-J03-XdsContentTypeCode-CISIS|20260223120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J03-XdsContentTypeCode-CISIS/FHIR/JDV-J03-XdsContentTypeCode-CISIS|20260928120000</t>
   </si>
   <si>
     <t>xdmSubmissionSet.contentType.code</t>
